--- a/ig/main/ValueSet-fr-core-insee-code.xlsx
+++ b/ig/main/ValueSet-fr-core-insee-code.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-09T09:28:26+00:00</t>
+    <t>2023-10-16T13:03:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-insee-code.xlsx
+++ b/ig/main/ValueSet-fr-core-insee-code.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T13:03:47+00:00</t>
+    <t>2023-10-16T13:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-insee-code.xlsx
+++ b/ig/main/ValueSet-fr-core-insee-code.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T13:05:21+00:00</t>
+    <t>2023-10-16T13:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-insee-code.xlsx
+++ b/ig/main/ValueSet-fr-core-insee-code.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.fr/ig/fhir/core/ValueSet/fr-core-insee-code</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-insee-code</t>
   </si>
   <si>
     <t>Identifier</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T13:49:57+00:00</t>
+    <t>2023-10-23T09:15:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-insee-code.xlsx
+++ b/ig/main/ValueSet-fr-core-insee-code.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-23T09:15:45+00:00</t>
+    <t>2023-10-23T11:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-insee-code.xlsx
+++ b/ig/main/ValueSet-fr-core-insee-code.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-23T11:28:06+00:00</t>
+    <t>2023-11-06T10:15:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-insee-code.xlsx
+++ b/ig/main/ValueSet-fr-core-insee-code.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-06T10:15:36+00:00</t>
+    <t>2023-11-07T09:05:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-insee-code.xlsx
+++ b/ig/main/ValueSet-fr-core-insee-code.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T09:05:25+00:00</t>
+    <t>2023-11-08T15:11:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-insee-code.xlsx
+++ b/ig/main/ValueSet-fr-core-insee-code.xlsx
@@ -7,13 +7,13 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from TRE-R13-CommuneO" r:id="rId4" sheetId="2"/>
+    <sheet name="Include from TRE-R13-Commune" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
   <si>
     <t>Property</t>
   </si>
@@ -60,10 +60,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T15:11:22+00:00</t>
+    <t>2023-11-21T10:12:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -108,7 +111,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R13-CommuneOM/FHIR/TRE-R13-CommuneOM</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R13-Commune/FHIR/TRE-R13-Commune</t>
   </si>
 </sst>
 </file>
@@ -309,66 +312,68 @@
       <c r="A8" t="s" s="2">
         <v>14</v>
       </c>
-      <c r="B8" s="2"/>
+      <c r="B8" t="s" s="2">
+        <v>15</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -387,28 +392,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/ValueSet-fr-core-insee-code.xlsx
+++ b/ig/main/ValueSet-fr-core-insee-code.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-21T10:12:39+00:00</t>
+    <t>2023-12-04T10:06:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-insee-code.xlsx
+++ b/ig/main/ValueSet-fr-core-insee-code.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-04T10:06:25+00:00</t>
+    <t>2023-12-04T12:30:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-insee-code.xlsx
+++ b/ig/main/ValueSet-fr-core-insee-code.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-04T12:30:51+00:00</t>
+    <t>2023-12-04T12:32:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-insee-code.xlsx
+++ b/ig/main/ValueSet-fr-core-insee-code.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
   <si>
     <t>Property</t>
   </si>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-04T12:32:37+00:00</t>
+    <t>2023-12-11T10:19:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -79,6 +79,12 @@
   </si>
   <si>
     <t>No display for ContactDetail</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>
@@ -245,7 +251,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -360,20 +366,28 @@
       <c r="A14" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="B16" t="s" s="2">
         <v>27</v>
+      </c>
+      <c r="B16" s="2"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -392,28 +406,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/ValueSet-fr-core-insee-code.xlsx
+++ b/ig/main/ValueSet-fr-core-insee-code.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T10:19:21+00:00</t>
+    <t>2023-12-11T10:51:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-insee-code.xlsx
+++ b/ig/main/ValueSet-fr-core-insee-code.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T10:51:09+00:00</t>
+    <t>2023-12-11T13:13:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-insee-code.xlsx
+++ b/ig/main/ValueSet-fr-core-insee-code.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-11T13:13:22+00:00</t>
+    <t>2023-12-19T10:49:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-insee-code.xlsx
+++ b/ig/main/ValueSet-fr-core-insee-code.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T10:49:53+00:00</t>
+    <t>2023-12-22T08:30:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-insee-code.xlsx
+++ b/ig/main/ValueSet-fr-core-insee-code.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-22T08:30:59+00:00</t>
+    <t>2024-01-19T16:14:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-insee-code.xlsx
+++ b/ig/main/ValueSet-fr-core-insee-code.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-19T16:14:08+00:00</t>
+    <t>2024-01-22T11:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-insee-code.xlsx
+++ b/ig/main/ValueSet-fr-core-insee-code.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-22T11:10:15+00:00</t>
+    <t>2024-01-22T11:10:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-insee-code.xlsx
+++ b/ig/main/ValueSet-fr-core-insee-code.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-22T11:10:58+00:00</t>
+    <t>2024-01-29T10:14:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-insee-code.xlsx
+++ b/ig/main/ValueSet-fr-core-insee-code.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T10:14:55+00:00</t>
+    <t>2024-01-29T10:26:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-insee-code.xlsx
+++ b/ig/main/ValueSet-fr-core-insee-code.xlsx
@@ -30,7 +30,7 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>id: urn:oid:2.16.840.1.113883.2.8.1.3.4</t>
+    <t>http://interopsante.org/fhir/ValueSet#urn:oid:2.16.840.1.113883.2.8.1.3.4</t>
   </si>
   <si>
     <t>Version</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T10:26:27+00:00</t>
+    <t>2024-02-05T10:12:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
